--- a/data/trans_dic/IP18A02-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP18A02-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por control de salud periódico</t>
+          <t>Menores que su última consulta al médico fue por control de salud periódico (tasa de respuesta: 98,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,37 +717,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>34,36; 49,46</t>
+          <t>33,37; 49,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>34,2; 47,55</t>
+          <t>34,0; 47,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37,87; 51,24</t>
+          <t>37,81; 51,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29,28; 63,68</t>
+          <t>28,87; 64,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>39,11; 55,25</t>
+          <t>39,58; 54,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,53; 44,85</t>
+          <t>31,33; 44,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,12; 51,93</t>
+          <t>35,97; 50,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -756,22 +757,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>39,25; 50,47</t>
+          <t>38,62; 49,84</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34,36; 44,09</t>
+          <t>34,09; 43,82</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39,04; 49,7</t>
+          <t>39,14; 48,98</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>33,2; 57,82</t>
+          <t>31,63; 57,66</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,52; 31,46</t>
+          <t>22,41; 31,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,89; 26,54</t>
+          <t>17,25; 26,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,24; 21,86</t>
+          <t>12,85; 21,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,48; 26,35</t>
+          <t>4,88; 27,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,83; 24,98</t>
+          <t>16,81; 24,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,37; 22,5</t>
+          <t>14,37; 22,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,06; 24,27</t>
+          <t>16,42; 24,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,18; 26,83</t>
+          <t>6,3; 26,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,5; 26,81</t>
+          <t>20,62; 27,04</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16,73; 22,67</t>
+          <t>16,53; 22,69</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,3; 22,27</t>
+          <t>15,93; 22,14</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,1; 22,62</t>
+          <t>8,21; 23,19</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,3; 25,55</t>
+          <t>13,56; 25,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,71; 19,25</t>
+          <t>9,72; 19,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,92; 18,33</t>
+          <t>9,84; 18,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,09; 23,8</t>
+          <t>3,01; 25,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,06; 19,05</t>
+          <t>9,39; 19,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,18; 17,28</t>
+          <t>8,54; 17,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,0; 13,71</t>
+          <t>5,96; 13,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,74; 24,77</t>
+          <t>5,01; 25,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,44; 20,23</t>
+          <t>12,22; 20,17</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10,31; 16,75</t>
+          <t>10,08; 16,61</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,69; 14,63</t>
+          <t>9,08; 15,17</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,06; 21,0</t>
+          <t>6,09; 20,39</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,46; 14,18</t>
+          <t>6,68; 14,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,67; 14,93</t>
+          <t>6,42; 14,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,42; 9,87</t>
+          <t>3,43; 9,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,37; 37,26</t>
+          <t>6,98; 34,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,4; 10,49</t>
+          <t>4,18; 10,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,19; 13,59</t>
+          <t>5,85; 13,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,86; 15,53</t>
+          <t>6,9; 14,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,21; 31,25</t>
+          <t>8,57; 31,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,26; 11,15</t>
+          <t>6,13; 11,17</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,3; 12,76</t>
+          <t>7,24; 12,87</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,0; 11,4</t>
+          <t>5,76; 11,34</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,78; 27,08</t>
+          <t>11,07; 29,45</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>20,49; 26,14</t>
+          <t>20,6; 26,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,62; 23,67</t>
+          <t>18,39; 23,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,35; 21,45</t>
+          <t>16,56; 21,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13,06; 25,97</t>
+          <t>13,49; 26,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,59; 22,95</t>
+          <t>17,85; 22,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,73; 21,33</t>
+          <t>16,33; 21,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,21; 22,19</t>
+          <t>17,29; 22,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,95; 25,5</t>
+          <t>13,64; 25,35</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,89; 23,62</t>
+          <t>19,73; 23,6</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18,19; 21,91</t>
+          <t>18,33; 21,93</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,69; 21,03</t>
+          <t>17,53; 21,15</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,12; 23,58</t>
+          <t>15,27; 23,54</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que su última consulta al médico fue por control de salud periódico (tasa de respuesta: 98,79%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>42218</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>57256</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>56891</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>7575</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>51158</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>53982</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>51738</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>7722</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>93376</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>111237</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>108630</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>15297</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>33947; 50512</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>47901; 67260</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>48194; 65492</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>4704; 10543</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>42625; 58819</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>44634; 64085</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>42374; 59574</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>5043; 10756</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>80863; 104353</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>96580; 124144</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>96010; 120159</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>10989; 20033</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>61567</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>46152</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>33044</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3585</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>48134</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>46220</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>48086</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>5049</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>109701</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>92372</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>81129</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>8634</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>51908; 72989</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>37921; 57340</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>24826; 41714</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1376; 7812</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>39231; 58019</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>36602; 58084</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>38784; 59033</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>2126; 8867</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>95886; 125730</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>78447; 107657</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>68396; 95057</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>5081; 14363</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>19981</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>20813</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>23316</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3558</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>15932</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>18673</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>15724</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>4572</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>35913</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>39486</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>39041</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>8130</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>14382; 26639</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>14601; 28830</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>16672; 31475</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>941; 7891</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>10866; 22824</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>12780; 26309</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>10026; 22544</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1849; 9277</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>27098; 44707</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>30237; 49811</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>30669; 51210</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>4151; 13902</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>15873</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>15589</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>8876</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4511</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>11342</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>15326</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>15486</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>7699</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>27215</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>30915</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>24362</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>12210</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>10605; 23061</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>9765; 22633</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>5185; 15103</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>1713; 8408</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>6996; 17237</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>9538; 22270</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>10194; 22094</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>3645; 13548</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>19980; 36404</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>22805; 40553</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>17230; 33906</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>7427; 19754</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>391</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>139640</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>139810</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>122128</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>19229</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>126565</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>134200</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>131035</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>25042</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>266205</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>274010</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>253163</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>44271</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>123195; 157361</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>121942; 157901</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>106202; 137208</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>13530; 26299</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>111383; 143189</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>115941; 151303</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>115814; 147761</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>17947; 33365</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>241130; 288357</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>251680; 301133</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>229916; 277317</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>35401; 54582</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP18A02-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP18A02-Edad-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>33,37; 49,66</t>
+          <t>33,67; 49,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>34,0; 47,75</t>
+          <t>33,87; 47,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37,81; 51,38</t>
+          <t>37,66; 51,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28,87; 64,7</t>
+          <t>29,86; 65,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>39,58; 54,62</t>
+          <t>39,31; 55,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,33; 44,99</t>
+          <t>31,6; 44,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,97; 50,56</t>
+          <t>36,56; 50,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>27,34; 58,31</t>
+          <t>26,57; 59,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>38,62; 49,84</t>
+          <t>39,37; 49,95</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34,09; 43,82</t>
+          <t>34,34; 44,48</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39,14; 48,98</t>
+          <t>38,99; 49,28</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>31,63; 57,66</t>
+          <t>32,24; 56,84</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,41; 31,52</t>
+          <t>22,38; 31,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,25; 26,09</t>
+          <t>16,72; 25,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,85; 21,6</t>
+          <t>13,22; 22,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,88; 27,7</t>
+          <t>4,62; 28,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,81; 24,86</t>
+          <t>16,3; 25,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,37; 22,8</t>
+          <t>14,79; 22,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,42; 24,99</t>
+          <t>16,32; 24,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,3; 26,29</t>
+          <t>7,42; 28,23</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,62; 27,04</t>
+          <t>20,3; 26,82</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16,53; 22,69</t>
+          <t>16,42; 22,23</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15,93; 22,14</t>
+          <t>15,96; 22,16</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,21; 23,19</t>
+          <t>8,28; 22,68</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,56; 25,12</t>
+          <t>13,45; 25,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,72; 19,19</t>
+          <t>9,71; 18,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,84; 18,57</t>
+          <t>9,78; 18,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,01; 25,21</t>
+          <t>4,24; 25,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,39; 19,73</t>
+          <t>9,37; 19,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,54; 17,58</t>
+          <t>8,36; 17,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,96; 13,41</t>
+          <t>5,95; 13,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,01; 25,16</t>
+          <t>5,69; 25,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,22; 20,17</t>
+          <t>12,41; 20,46</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10,08; 16,61</t>
+          <t>10,22; 16,47</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,08; 15,17</t>
+          <t>9,0; 14,56</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,09; 20,39</t>
+          <t>5,86; 20,76</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,68; 14,53</t>
+          <t>6,68; 14,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,42; 14,87</t>
+          <t>6,69; 14,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,43; 9,99</t>
+          <t>3,16; 9,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,98; 34,28</t>
+          <t>6,46; 36,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,18; 10,31</t>
+          <t>4,2; 10,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,85; 13,67</t>
+          <t>6,01; 13,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,9; 14,95</t>
+          <t>6,75; 15,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,57; 31,84</t>
+          <t>8,92; 32,5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,13; 11,17</t>
+          <t>6,19; 10,99</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,24; 12,87</t>
+          <t>7,42; 13,02</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,76; 11,34</t>
+          <t>5,74; 11,13</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,07; 29,45</t>
+          <t>10,48; 27,76</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>20,6; 26,31</t>
+          <t>20,62; 26,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,39; 23,81</t>
+          <t>18,41; 23,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,56; 21,4</t>
+          <t>16,58; 21,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13,49; 26,22</t>
+          <t>13,56; 26,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,85; 22,95</t>
+          <t>17,79; 22,97</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,33; 21,32</t>
+          <t>16,39; 21,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,29; 22,06</t>
+          <t>16,97; 21,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,64; 25,35</t>
+          <t>14,04; 24,96</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,73; 23,6</t>
+          <t>20,12; 23,92</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18,33; 21,93</t>
+          <t>18,23; 21,91</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,53; 21,15</t>
+          <t>17,62; 21,17</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,27; 23,54</t>
+          <t>14,7; 23,52</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>33947; 50512</t>
+          <t>34248; 49939</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>47901; 67260</t>
+          <t>47708; 66673</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>48194; 65492</t>
+          <t>48014; 65515</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4704; 10543</t>
+          <t>4865; 10627</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>42625; 58819</t>
+          <t>42333; 59738</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>44634; 64085</t>
+          <t>45014; 63742</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>42374; 59574</t>
+          <t>43078; 59876</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5043; 10756</t>
+          <t>4902; 10974</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>80863; 104353</t>
+          <t>82440; 104587</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>96580; 124144</t>
+          <t>97278; 126028</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>96010; 120159</t>
+          <t>95647; 120886</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10989; 20033</t>
+          <t>11202; 19746</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>51908; 72989</t>
+          <t>51829; 71879</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37921; 57340</t>
+          <t>36751; 55642</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24826; 41714</t>
+          <t>25532; 43463</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1376; 7812</t>
+          <t>1302; 8061</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>39231; 58019</t>
+          <t>38053; 58471</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36602; 58084</t>
+          <t>37679; 57544</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38784; 59033</t>
+          <t>38556; 58404</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2126; 8867</t>
+          <t>2504; 9522</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>95886; 125730</t>
+          <t>94407; 124714</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>78447; 107657</t>
+          <t>77912; 105474</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>68396; 95057</t>
+          <t>68521; 95132</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5081; 14363</t>
+          <t>5130; 14047</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14382; 26639</t>
+          <t>14263; 27513</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14601; 28830</t>
+          <t>14583; 28344</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16672; 31475</t>
+          <t>16571; 30886</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>941; 7891</t>
+          <t>1328; 7845</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10866; 22824</t>
+          <t>10834; 22903</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12780; 26309</t>
+          <t>12509; 25957</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10026; 22544</t>
+          <t>10010; 22180</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1849; 9277</t>
+          <t>2100; 9219</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>27098; 44707</t>
+          <t>27522; 45363</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30237; 49811</t>
+          <t>30656; 49398</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30669; 51210</t>
+          <t>30392; 49162</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4151; 13902</t>
+          <t>3995; 14150</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10605; 23061</t>
+          <t>10597; 22741</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9765; 22633</t>
+          <t>10185; 22125</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5185; 15103</t>
+          <t>4773; 14379</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1713; 8408</t>
+          <t>1584; 8854</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6996; 17237</t>
+          <t>7028; 17023</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9538; 22270</t>
+          <t>9799; 22588</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10194; 22094</t>
+          <t>9968; 23016</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3645; 13548</t>
+          <t>3794; 13827</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19980; 36404</t>
+          <t>20179; 35814</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22805; 40553</t>
+          <t>23373; 41044</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17230; 33906</t>
+          <t>17157; 33262</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7427; 19754</t>
+          <t>7031; 18616</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>123195; 157361</t>
+          <t>123311; 156291</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>121942; 157901</t>
+          <t>122091; 157209</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>106202; 137208</t>
+          <t>106331; 139069</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13530; 26299</t>
+          <t>13605; 26560</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>111383; 143189</t>
+          <t>110984; 143305</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>115941; 151303</t>
+          <t>116359; 152330</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>115814; 147761</t>
+          <t>113675; 147131</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>17947; 33365</t>
+          <t>18472; 32847</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>241130; 288357</t>
+          <t>245853; 292357</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>251680; 301133</t>
+          <t>250288; 300829</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>229916; 277317</t>
+          <t>231019; 277629</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>35401; 54582</t>
+          <t>34095; 54546</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP18A02-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP18A02-Edad-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por control de salud periódico (tasa de respuesta: 98,79%)</t>
+          <t>Menores cuya última consulta médica fue por control de salud periódico (tasa de respuesta: 98,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>47,51%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>37,9%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>43,91%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>42,57%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>41,51%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>40,64%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>44,63%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>46,49%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>47,51%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>37,9%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>43,91%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>45,26%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>33,67; 49,1</t>
+          <t>39,11; 55,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>33,87; 47,33</t>
+          <t>31,53; 44,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37,66; 51,39</t>
+          <t>37,12; 51,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29,86; 65,22</t>
+          <t>26,75; 58,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>39,31; 55,48</t>
+          <t>34,36; 49,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,6; 44,75</t>
+          <t>34,2; 47,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,56; 50,82</t>
+          <t>37,87; 51,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>26,57; 59,49</t>
+          <t>29,49; 65,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>39,37; 49,95</t>
+          <t>39,25; 50,47</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34,34; 44,48</t>
+          <t>34,36; 44,09</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38,99; 49,28</t>
+          <t>39,04; 49,7</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>32,24; 56,84</t>
+          <t>34,49; 58,87</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>20,62%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>18,14%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>20,35%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>15,13%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>26,59%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>21,0%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>17,11%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>12,71%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>20,62%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>18,14%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>20,35%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,58%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,38; 31,04</t>
+          <t>16,83; 24,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,72; 25,31</t>
+          <t>14,37; 22,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,22; 22,5</t>
+          <t>16,06; 24,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,62; 28,59</t>
+          <t>7,22; 28,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,3; 25,05</t>
+          <t>22,52; 31,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,79; 22,59</t>
+          <t>16,89; 26,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,32; 24,72</t>
+          <t>13,24; 21,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,42; 28,23</t>
+          <t>6,03; 27,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,3; 26,82</t>
+          <t>20,5; 26,81</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16,42; 22,23</t>
+          <t>16,73; 22,67</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15,96; 22,16</t>
+          <t>16,3; 22,27</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,28; 22,68</t>
+          <t>8,44; 23,5</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>13,77%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>12,48%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9,35%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>13,29%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>18,84%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>13,86%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>13,76%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>11,37%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>13,77%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>12,48%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>9,35%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,94%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,45; 25,95</t>
+          <t>9,06; 19,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,71; 18,87</t>
+          <t>8,18; 17,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,78; 18,22</t>
+          <t>6,0; 13,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,24; 25,07</t>
+          <t>5,09; 26,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,37; 19,8</t>
+          <t>13,3; 25,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,36; 17,34</t>
+          <t>9,71; 19,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,95; 13,19</t>
+          <t>9,92; 18,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,69; 25,0</t>
+          <t>4,56; 25,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,41; 20,46</t>
+          <t>12,44; 20,23</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10,22; 16,47</t>
+          <t>10,31; 16,75</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,0; 14,56</t>
+          <t>8,69; 14,63</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,86; 20,76</t>
+          <t>6,49; 22,29</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6,78%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9,4%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>10,48%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>18,94%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>10,0%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>10,24%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>5,87%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>18,39%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6,78%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9,4%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>10,48%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>19,24%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,68; 14,33</t>
+          <t>4,4; 10,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,69; 14,54</t>
+          <t>6,19; 13,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,16; 9,51</t>
+          <t>6,86; 15,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,46; 36,1</t>
+          <t>9,78; 32,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,2; 10,18</t>
+          <t>6,46; 14,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,01; 13,86</t>
+          <t>6,67; 14,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,75; 15,58</t>
+          <t>3,42; 9,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,92; 32,5</t>
+          <t>7,9; 40,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,19; 10,99</t>
+          <t>6,26; 11,15</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,42; 13,02</t>
+          <t>7,3; 12,76</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,74; 11,13</t>
+          <t>6,0; 11,4</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,48; 27,76</t>
+          <t>11,36; 28,82</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>20,28%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>18,91%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>19,56%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>19,36%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>23,35%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>21,09%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>19,04%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>19,17%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>20,28%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>18,91%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>19,56%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,82%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>20,62; 26,13</t>
+          <t>17,59; 22,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,41; 23,71</t>
+          <t>16,73; 21,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,58; 21,69</t>
+          <t>17,21; 22,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13,56; 26,48</t>
+          <t>14,2; 26,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,79; 22,97</t>
+          <t>20,49; 26,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,39; 21,46</t>
+          <t>18,62; 23,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,97; 21,96</t>
+          <t>16,35; 21,45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,04; 24,96</t>
+          <t>13,93; 27,68</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20,12; 23,92</t>
+          <t>19,89; 23,62</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18,23; 21,91</t>
+          <t>18,19; 21,91</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,62; 21,17</t>
+          <t>17,69; 21,03</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,7; 23,52</t>
+          <t>15,77; 24,6</t>
         </is>
       </c>
     </row>
@@ -1387,13 +1387,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por control de salud periódico (tasa de respuesta: 98,79%)</t>
+          <t>Menores cuya última consulta médica fue por control de salud periódico (tasa de respuesta: 98,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>84</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>91</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>51158</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>53982</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>51738</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>6536</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>42218</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>57256</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>56891</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>7575</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>51158</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>53982</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>51738</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7722</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15297</t>
+          <t>13769</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>34248; 49939</t>
+          <t>42118; 59494</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>47708; 66673</t>
+          <t>44908; 63893</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>48014; 65515</t>
+          <t>43735; 61181</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4865; 10627</t>
+          <t>4106; 8990</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>42333; 59738</t>
+          <t>34944; 50307</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>45014; 63742</t>
+          <t>48183; 66988</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43078; 59876</t>
+          <t>48277; 65324</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4902; 10974</t>
+          <t>4443; 9915</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>82440; 104587</t>
+          <t>82192; 105680</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>97278; 126028</t>
+          <t>97346; 124917</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>95647; 120886</t>
+          <t>95765; 121902</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11202; 19746</t>
+          <t>10491; 17908</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>48134</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>46220</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>48086</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4411</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>61567</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>46152</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>33044</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3585</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>48134</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>46220</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>48086</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5049</t>
+          <t>3540</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8634</t>
+          <t>7951</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>51829; 71879</t>
+          <t>39275; 58307</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>36751; 55642</t>
+          <t>36609; 57307</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25532; 43463</t>
+          <t>37953; 57329</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1302; 8061</t>
+          <t>2103; 8360</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>38053; 58471</t>
+          <t>52150; 72854</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37679; 57544</t>
+          <t>37133; 58346</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38556; 58404</t>
+          <t>25579; 42227</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2504; 9522</t>
+          <t>1531; 7051</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>94407; 124714</t>
+          <t>95340; 124659</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>77912; 105474</t>
+          <t>79397; 107566</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>68521; 95132</t>
+          <t>69974; 95641</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5130; 14047</t>
+          <t>4606; 12820</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>15932</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>18673</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>15724</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4727</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>19981</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>20813</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>23316</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>3558</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>15932</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>18673</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>15724</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4572</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>8429</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14263; 27513</t>
+          <t>10475; 22030</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14583; 28344</t>
+          <t>12247; 25870</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16571; 30886</t>
+          <t>10087; 23046</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1328; 7845</t>
+          <t>1810; 9509</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10834; 22903</t>
+          <t>14102; 27088</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12509; 25957</t>
+          <t>14581; 28909</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10010; 22180</t>
+          <t>16813; 31062</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2100; 9219</t>
+          <t>1346; 7517</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>27522; 45363</t>
+          <t>27574; 44846</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30656; 49398</t>
+          <t>30933; 50224</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30392; 49162</t>
+          <t>29350; 49397</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3995; 14150</t>
+          <t>4227; 14514</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>11342</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>15326</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>15486</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>7892</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>15873</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>15589</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>8876</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4511</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>11342</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>15326</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>15486</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>7699</t>
+          <t>5025</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12210</t>
+          <t>12917</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10597; 22741</t>
+          <t>7358; 17544</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10185; 22125</t>
+          <t>10084; 22140</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4773; 14379</t>
+          <t>10136; 22944</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1584; 8854</t>
+          <t>4074; 13501</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7028; 17023</t>
+          <t>10246; 22504</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9799; 22588</t>
+          <t>10147; 22721</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9968; 23016</t>
+          <t>5174; 14926</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3794; 13827</t>
+          <t>2014; 10351</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20179; 35814</t>
+          <t>20412; 36339</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>23373; 41044</t>
+          <t>23013; 40223</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17157; 33262</t>
+          <t>17937; 34075</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7031; 18616</t>
+          <t>7630; 19351</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>212</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>201</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>189</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>30</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>126565</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>134200</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>131035</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>23565</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>139640</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>139810</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>122128</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>19229</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>126565</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>134200</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>131035</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>25042</t>
+          <t>19500</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>44271</t>
+          <t>43065</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>123311; 156291</t>
+          <t>109774; 143230</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>122091; 157209</t>
+          <t>118759; 151405</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>106331; 139069</t>
+          <t>115286; 148676</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13605; 26560</t>
+          <t>17290; 32281</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>110984; 143305</t>
+          <t>122547; 156306</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>116359; 152330</t>
+          <t>123450; 156938</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>113675; 147131</t>
+          <t>104847; 137562</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>18472; 32847</t>
+          <t>13305; 26436</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>245853; 292357</t>
+          <t>243041; 288656</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>250288; 300829</t>
+          <t>249664; 300786</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>231019; 277629</t>
+          <t>231902; 275777</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>34095; 54546</t>
+          <t>34266; 53446</t>
         </is>
       </c>
     </row>
